--- a/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
+++ b/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
@@ -1514,12 +1514,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>项目组确认</t>
+          <t>项目组向公司问询取得</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>公司／客户结构／截至 2026 年 9 月；定稿前需经企业书面确认</t>
+          <t>公司／客户结构／截至 2026 年 9 月。所列为问询所得，是否为全部客户未作确认；正文按“客户结构”列示，不作封闭表述，后续补充客户可直接追加</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>公司／全部专利／截至 2026 年 9 月；授权与申请分别列示，不混用</t>
+          <t>公司／全部专利／截至 2026 年 9 月；授权与申请分别列示，不混用。现取企查查整理版，尚未逐项回国家知识产权局原库比对</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">

--- a/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
+++ b/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -894,7 +894,37 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>表3；核心技术</t>
+          <t>表4；核心技术</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>江丰电子、珂玛科技、先锋精科、臻宝科技、托伦斯、中瓷电子 2026 年半年度报告</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>各公司</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>定期报告</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>巨潮资讯网／交易所网站</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>表2；图1；市场竞争</t>
         </is>
       </c>
     </row>
@@ -909,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1307,7 +1337,7 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>图1；发展趋势</t>
+          <t>图2；发展趋势</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1339,7 +1369,7 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>图1</t>
+          <t>图2</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1499,7 +1529,7 @@
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>表2；客户开拓</t>
+          <t>表3；客户开拓</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1531,7 +1561,7 @@
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>表2；客户开拓</t>
+          <t>表3；客户开拓</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1563,94 +1593,190 @@
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>表3；核心技术</t>
+          <t>图1；市场竞争</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>专利 73 项，有效授权 56 项（发明 19 项、实用新型 35 项、外观设计 3 项），审查中 14 项</t>
+          <t>五家可比公司 2026 年 1—6 月零部件业务收入：江丰电子精密零部件 6.45 亿元、珂玛科技先进陶瓷材料零部件 5.43 亿元、先锋精科工艺部件 4.72 亿元、臻宝科技泛半导体零部件 4.02 亿元、托伦斯半导体工艺零部件 2.39 亿元</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>国家知识产权局</t>
+          <t>各公司</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>经企查查整理</t>
+          <t>2026 年半年度报告</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>公司／全部专利／截至 2026 年 9 月；授权与申请分别列示，不混用。现取企查查整理版，尚未逐项回国家知识产权局原库比对</t>
+          <t>各公司／各自披露的零部件业务分类／2026 年 1—6 月；口径逐家不同，图注中分别列明。富创精密未披露分业务数据，未予列示</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>核心技术</t>
+          <t>表2；市场竞争</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>氮化铝陶瓷加热盘已实现量产</t>
+          <t>珂玛科技部分陶瓷加热器已量产、新增产能 600 只／年；中瓷电子具备 6/8/12 英寸静电卡盘及加热盘批量生产能力；先锋精科陶瓷加热器在客户端验证、尚未产生收入</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>项目组</t>
+          <t>各公司</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>项目组确认</t>
+          <t>2026 年半年度报告</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>公司／加热盘产品线／截至 2026 年 9 月</t>
+          <t>各公司／陶瓷加热盘产品线／2026 年 1—6 月</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>不进正文（内部判断依据）</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>五家可比公司 2026 年 1—6 月零部件业务毛利率：江丰电子 23.97%、托伦斯 26.65%、先锋精科 28.10%（以上金属路线）；珂玛科技 48.51%、臻宝科技 50.65%（以上非金属路线）。同一公司内部同样分层：先锋精科工艺部件 28.10%、结构部件 16.71%；托伦斯工艺零部件 26.65%、结构零部件 17.93%</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>各公司</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2026 年半年度报告</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>各公司／各自披露的零部件业务分类／2026 年 1—6 月。先锋精科、臻宝科技由收入与成本测算，与托伦斯、珂玛科技、江丰电子的披露值交叉验证一致。用于估值对标与拜访提问，不进交付物正文</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>表4；核心技术</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>专利 73 项，有效授权 56 项（发明 19 项、实用新型 35 项、外观设计 3 项），审查中 14 项</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>国家知识产权局</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>经企查查整理</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>公司／全部专利／截至 2026 年 9 月；授权与申请分别列示，不混用。现取企查查整理版，尚未逐项回国家知识产权局原库比对</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>核心技术</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>氮化铝陶瓷加热盘已实现量产</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>项目组</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>项目组确认</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>公司／加热盘产品线／截至 2026 年 9 月</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>核心技术</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>“半导体薄膜沉积设备高精密气体喷淋头”列入目录“两新”技术产品第 189 项，该册共 1,739 项</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>江苏省工业和信息化厅</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>苏工信创新〔2025〕224 号及所附目录</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>江苏省／“两新”技术产品册／2025 年，两年内有效</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2100,7 +2226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2197,17 +2323,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>技术指标（加工精度 ±0.003—0.005mm、表面粗糙度 Ra≤0.1μm、Y₂O₃ 涂层寿命 3,000→12,000 小时、温度偏差 ≤±1℃）</t>
+          <t>中瓷电子“已突破 144 区多区控温并进入长江存储供应链验证”</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>公开检索；未见发布机构</t>
+          <t>中瓷电子 2026 年半年度报告</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>已从正文删除，改用 QYResearch 原件的定性趋势表述</t>
+          <t>半年报中无此表述，已从正文删除；改用其披露的“具备 6/8/12 英寸静电卡盘及加热盘批量生产能力”</t>
         </is>
       </c>
     </row>
@@ -2217,17 +2343,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>各生产基地的产品分工与产能（合肥 45 万件/年→100 万件/年；无锡 30 万套/年密封组件）</t>
+          <t>技术指标（加工精度 ±0.003—0.005mm、表面粗糙度 Ra≤0.1μm、Y₂O₃ 涂层寿命 3,000→12,000 小时、温度偏差 ≤±1℃）</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>公开报道、行业媒体、政府招商发布</t>
+          <t>公开检索；未见发布机构</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>三个公开口径互相冲突（无锡基地在两处分别被表述为金属件基地与密封件基地），已从正文删除，仅保留基地所在城市</t>
+          <t>已从正文删除，改用 QYResearch 原件的定性趋势表述</t>
         </is>
       </c>
     </row>
@@ -2237,17 +2363,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>武汉葛店基地零部件清洗业务月均处理量 5,000 余件</t>
+          <t>各生产基地的产品分工与产能（合肥 45 万件/年→100 万件/年；无锡 30 万套/年密封组件）</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>公开报道</t>
+          <t>公开报道、行业媒体、政府招商发布</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>仅见报道转述，且清洗业务非本材料主线，已从正文删除</t>
+          <t>三个公开口径互相冲突（无锡基地在两处分别被表述为金属件基地与密封件基地），已从正文删除，仅保留基地所在城市</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2383,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>武汉葛店工厂项目总投资额</t>
+          <t>武汉葛店基地零部件清洗业务月均处理量 5,000 余件</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2267,7 +2393,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>存在两个冲突口径；本材料四节不涉及资本开支，未采用</t>
+          <t>仅见报道转述，且清洗业务非本材料主线，已从正文删除</t>
         </is>
       </c>
     </row>
@@ -2277,15 +2403,35 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>武汉葛店工厂项目总投资额</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>存在两个冲突口径；本材料四节不涉及资本开支，未采用</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>清洗业务客户是否包含三安光电、瑞华光电</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>公开报道</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>属化合物半导体与 LED 领域，非公司主线业务，未采用</t>
         </is>

--- a/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
+++ b/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
@@ -924,7 +924,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>表2；图1；市场竞争</t>
+          <t>表2；市场竞争</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>图2；发展趋势</t>
+          <t>图1；发展趋势</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>图2</t>
+          <t>图1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1593,7 +1593,7 @@
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>图1；市场竞争</t>
+          <t>不进正文（内部判断依据）</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>各公司／各自披露的零部件业务分类／2026 年 1—6 月；口径逐家不同，图注中分别列明。富创精密未披露分业务数据，未予列示</t>
+          <t>各公司／各自披露的零部件业务分类／2026 年 1—6 月；口径逐家不同。富创精密未披露分业务数据。原拟入图，因在“市场竞争”一节不承担论证而撤下</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">

--- a/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
+++ b/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>表4；核心技术</t>
+          <t>表5；核心技术</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>表2；市场竞争</t>
+          <t>表3；市场竞争</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1529,7 +1529,7 @@
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>表3；客户开拓</t>
+          <t>表4；客户开拓</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>表3；客户开拓</t>
+          <t>表4；客户开拓</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>珂玛科技部分陶瓷加热器已量产、新增产能 600 只／年；中瓷电子具备 6/8/12 英寸静电卡盘及加热盘批量生产能力；先锋精科陶瓷加热器在客户端验证、尚未产生收入</t>
+          <t>富创精密报告期内完成多款新型匀气盘研发落地、匀气盘业务同比翻倍、复杂结构产品已在国内先进制程领域导入与推广；先锋精科匀气盘为半导体类主要产品之一，微孔孔径标准差可达 0.3 微米（原文为“千万级微孔孔径标准差可达到 0.3μm”，指加工能力，非单片孔数）</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>各公司／陶瓷加热盘产品线／2026 年 1—6 月</t>
+          <t>各公司／匀气盘产品线／2026 年 1—6 月。富创精密未披露匀气盘收入金额，仅披露同比翻倍</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>不进正文（内部判断依据）</t>
+          <t>表2 注；市场竞争</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>五家可比公司 2026 年 1—6 月零部件业务毛利率：江丰电子 23.97%、托伦斯 26.65%、先锋精科 28.10%（以上金属路线）；珂玛科技 48.51%、臻宝科技 50.65%（以上非金属路线）。同一公司内部同样分层：先锋精科工艺部件 28.10%、结构部件 16.71%；托伦斯工艺零部件 26.65%、结构零部件 17.93%</t>
+          <t>江丰电子将气体分配盘、功能盘体、圆环类组件等金属件列为“国内供应链仍处于持续突破阶段”</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>各公司</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>各公司／各自披露的零部件业务分类／2026 年 1—6 月。先锋精科、臻宝科技由收入与成本测算，与托伦斯、珂玛科技、江丰电子的披露值交叉验证一致。用于估值对标与拜访提问，不进交付物正文</t>
+          <t>江丰电子／对行业的判断，非其自身产品进展／2026 年 1—6 月</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1689,94 +1689,158 @@
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>表4；核心技术</t>
+          <t>表3；市场竞争</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>专利 73 项，有效授权 56 项（发明 19 项、实用新型 35 项、外观设计 3 项），审查中 14 项</t>
+          <t>珂玛科技部分陶瓷加热器已量产、新增产能 600 只／年；中瓷电子具备 6/8/12 英寸静电卡盘及加热盘批量生产能力；先锋精科陶瓷加热器在客户端验证、尚未产生收入</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>国家知识产权局</t>
+          <t>各公司</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>经企查查整理</t>
+          <t>2026 年半年度报告</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>公司／全部专利／截至 2026 年 9 月；授权与申请分别列示，不混用。现取企查查整理版，尚未逐项回国家知识产权局原库比对</t>
+          <t>各公司／陶瓷加热盘产品线／2026 年 1—6 月</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>核心技术</t>
+          <t>不进正文（内部判断依据）</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>氮化铝陶瓷加热盘已实现量产</t>
+          <t>五家可比公司 2026 年 1—6 月零部件业务毛利率：江丰电子 23.97%、托伦斯 26.65%、先锋精科 28.10%（以上金属路线）；珂玛科技 48.51%、臻宝科技 50.65%（以上非金属路线）。同一公司内部同样分层：先锋精科工艺部件 28.10%、结构部件 16.71%；托伦斯工艺零部件 26.65%、结构零部件 17.93%</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>项目组</t>
+          <t>各公司</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>项目组确认</t>
+          <t>2026 年半年度报告</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>公司／加热盘产品线／截至 2026 年 9 月</t>
+          <t>各公司／各自披露的零部件业务分类／2026 年 1—6 月。先锋精科、臻宝科技由收入与成本测算，与托伦斯、珂玛科技、江丰电子的披露值交叉验证一致。用于估值对标与拜访提问，不进交付物正文</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>表5；核心技术</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>专利 73 项，有效授权 56 项（发明 19 项、实用新型 35 项、外观设计 3 项），审查中 14 项</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>国家知识产权局</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>经企查查整理</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>公司／全部专利／截至 2026 年 9 月；授权与申请分别列示，不混用。现取企查查整理版，尚未逐项回国家知识产权局原库比对</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>核心技术</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>氮化铝陶瓷加热盘已实现量产</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>项目组</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>项目组确认</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>公司／加热盘产品线／截至 2026 年 9 月</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>核心技术</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>“半导体薄膜沉积设备高精密气体喷淋头”列入目录“两新”技术产品第 189 项，该册共 1,739 项</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>江苏省工业和信息化厅</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>苏工信创新〔2025〕224 号及所附目录</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>江苏省／“两新”技术产品册／2025 年，两年内有效</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>

--- a/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
+++ b/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>专利 73 项，有效授权 56 项（发明 19 项、实用新型 35 项、外观设计 3 项），审查中 14 项</t>
+          <t>专利 73 项（发明 19、实用新型 35、发明公布 16、外观设计 3）；有效授权 56 项（发明 19、实用新型 34、外观设计 3）；发明公布中 13 项在实质审查</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2501,6 +2501,46 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>4 项专利（实用新型 1 项、发明公布 3 项）的法律状态</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>企查查整理版专利清单</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>73 项减去有效授权 56 项余 17 项，其中仅 13 项明确处于实质审查；正文改为只写 73 项与有效授权 56 项，不写审查中件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>零部件更换周期（密封件一至三个月、喷淋头六至十二个月）、2025 年设备厂商收入增速与零部件企业利润增速的对比、头部设备商先进制程静电卡盘与加热盘以自研为主</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>公开检索；三条均取自新稿，未见发布机构</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>暂留正文，定稿前需回原件或改为不带数字的定性表述</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
+++ b/output/金源/专题/无锡金源半导体专题材料_数据来源清单.xlsx
@@ -2290,7 +2290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2527,15 +2527,35 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>密封件门板的供货形态：整体供货（含金属门板本体）还是仅供门板上的密封件</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>公司官网产品中心（列有方形门板、圆形门板）；五家可比公司均无同类分产品披露</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>门板本体属金属结构件、随设备生命周期，其上的密封件属耗材，两者收入形态不同；公开统计未单列该品类，本材料四节不展开，正文表述为「三条主力产品线」</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>零部件更换周期（密封件一至三个月、喷淋头六至十二个月）、2025 年设备厂商收入增速与零部件企业利润增速的对比、头部设备商先进制程静电卡盘与加热盘以自研为主</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>公开检索；三条均取自新稿，未见发布机构</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>暂留正文，定稿前需回原件或改为不带数字的定性表述</t>
         </is>
